--- a/artfynd/A 23601-2026 artfynd.xlsx
+++ b/artfynd/A 23601-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>57642250</v>
+        <v>57642261</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576595.052359654</v>
+        <v>576421</v>
       </c>
       <c r="R2" t="n">
-        <v>6712247.240753895</v>
+        <v>6712223</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -748,19 +743,9 @@
           <t>2014-09-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -793,15 +778,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>57642270</v>
+        <v>131602636</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,37 +789,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Linderåsgruvan 1, Gstr</t>
+          <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576365.0824256439</v>
+        <v>576455</v>
       </c>
       <c r="R3" t="n">
-        <v>6712210.865395118</v>
+        <v>6712254</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,27 +843,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2014-09-01</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Observatör: Tommy Pettersson</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,16 +870,15 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AR3" t="inlineStr"/>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Tomas Troschke</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -914,12 +888,7 @@
         <v>57642269</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -951,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576463.8303648968</v>
+        <v>576464</v>
       </c>
       <c r="R4" t="n">
-        <v>6712180.960365671</v>
+        <v>6712181</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -984,19 +953,9 @@
           <t>2014-09-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1029,37 +988,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>57642267</v>
+        <v>57642270</v>
       </c>
       <c r="B5" t="n">
-        <v>86130</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>239209</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kantarellvaxskivling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hygrocybe cantharellus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1069,10 +1023,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576400.773495876</v>
+        <v>576365</v>
       </c>
       <c r="R5" t="n">
-        <v>6712201.775916344</v>
+        <v>6712211</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1102,19 +1056,9 @@
           <t>2014-09-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1147,53 +1091,57 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>57642271</v>
+        <v>1147788</v>
       </c>
       <c r="B6" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Linderåsgruvan 1, Gstr</t>
+          <t>Linderåsen, Gstr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576372.1829183269</v>
+        <v>576545</v>
       </c>
       <c r="R6" t="n">
-        <v>6712154.900416205</v>
+        <v>6712372</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1217,27 +1165,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2014-09-01</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-08-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Observatör: Tommy Pettersson</t>
+          <t>2011-08-08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,53 +1182,52 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AR6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Granskog, mossa</t>
+        </is>
+      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Lena Melin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Tomas Troschke</t>
+          <t>Lena Melin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>57642261</v>
+        <v>57642271</v>
       </c>
       <c r="B7" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1305,10 +1237,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576421.0343613272</v>
+        <v>576372</v>
       </c>
       <c r="R7" t="n">
-        <v>6712222.878662822</v>
+        <v>6712155</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1338,19 +1270,9 @@
           <t>2014-09-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1386,7 +1308,7 @@
         <v>131602649</v>
       </c>
       <c r="B8" t="n">
-        <v>57914</v>
+        <v>57975</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1497,6 +1419,427 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131602676</v>
+      </c>
+      <c r="B9" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hästkällan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>576425</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6712244</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>57642250</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Linderåsgruvan 1, Gstr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>576595</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6712247</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2014-09-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Observatör: Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Via Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>57642258</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Linderåsgruvan 1, Gstr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>576360</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6712219</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2014-09-01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Observatör: Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Via Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>57642267</v>
+      </c>
+      <c r="B12" t="n">
+        <v>89079</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>239209</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kantarellvaxing</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hygrocybe cantharellus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Linderåsgruvan 1, Gstr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>576401</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6712202</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2014-09-01</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Observatör: Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Via Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23601-2026 artfynd.xlsx
+++ b/artfynd/A 23601-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -775,6 +780,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57642261</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131602636</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57642269</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57642270</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1199,6 +1224,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1147788</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1302,6 +1332,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57642271</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1419,6 +1454,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131602649</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1531,6 +1571,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131602676</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1634,6 +1679,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57642250</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1737,6 +1787,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57642258</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1840,8 +1895,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57642267</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>